--- a/XLibur.Tests/Resource/Examples/PageSetup/HeaderFooters.xlsx
+++ b/XLibur.Tests/Resource/Examples/PageSetup/HeaderFooters.xlsx
@@ -360,16 +360,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:headerFooter scaleWithDoc="0" alignWithMargins="0">
     <x:oddHeader>&amp;LCreated with XLibur</x:oddHeader>
     <x:oddFooter>&amp;C&amp;P / &amp;N&amp;R&amp;Z&amp;F</x:oddFooter>
     <x:evenHeader>&amp;LCreated with XLibur</x:evenHeader>
@@ -377,6 +372,5 @@
     <x:firstHeader>&amp;LCreated with XLibur&amp;R&amp;"-,Bold"The &amp;"-,Regular"&amp;KFF0000First &amp;"-,Regular"&amp;E&amp;K0000FFColorful &amp;E&amp;"Broadway,Bold Italic"&amp;K000000Page</x:firstHeader>
     <x:firstFooter>&amp;C&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>